--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R32e33c8de1584bba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R065f437ea54d41d1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R065f437ea54d41d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf93b939bef7144e1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf93b939bef7144e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R351b0ac288834dde"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R351b0ac288834dde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R38875a9529ba4660"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R38875a9529ba4660"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R76c60aaa2d7c4d26"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R76c60aaa2d7c4d26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6a1e5a6aba9f45c9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6a1e5a6aba9f45c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra78c659502ad4e9d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra78c659502ad4e9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf778bc9c25c045ba"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf778bc9c25c045ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6819a9bbbe9444f7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6819a9bbbe9444f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5a98e7bfdeee4449"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5a98e7bfdeee4449"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb69e238ece7446fc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb69e238ece7446fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcf0ad1f22d65498c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcf0ad1f22d65498c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0cca87b782a94228"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0cca87b782a94228"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1e828906a0c446b9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1e828906a0c446b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R201de2f62dc64a99"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R201de2f62dc64a99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1a59242b219149c2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale2/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1a59242b219149c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5c8ccb9e92ff440b"/>
   </x:sheets>
 </x:workbook>
 </file>
